--- a/AI-safe-monthly-processing-data.xlsx
+++ b/AI-safe-monthly-processing-data.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1518" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1524" uniqueCount="71">
   <si>
     <t>TM</t>
   </si>
@@ -312,14 +312,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FFAD5C8A-8E97-4965-B69B-A83B8F46EFFC}" name="Table2" displayName="Table2" ref="A1:F60" totalsRowShown="0">
-  <autoFilter ref="A1:F60" xr:uid="{FFAD5C8A-8E97-4965-B69B-A83B8F46EFFC}"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FFAD5C8A-8E97-4965-B69B-A83B8F46EFFC}" name="Table2" displayName="Table2" ref="A1:G60" totalsRowShown="0">
+  <autoFilter ref="A1:G60" xr:uid="{FFAD5C8A-8E97-4965-B69B-A83B8F46EFFC}"/>
+  <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{4661BF11-588D-4BCE-A06F-1E4BDF679AE6}" name="TM"/>
     <tableColumn id="2" xr3:uid="{2A6CD833-E623-499F-B400-F67B45D93EEE}" name="Shift"/>
     <tableColumn id="3" xr3:uid="{975D7706-D81D-46A4-BB78-EA26FFE1F399}" name="Palletize (units)"/>
     <tableColumn id="4" xr3:uid="{AA2E891B-C401-41CD-9AF5-BBB84A42FBBA}" name="Zone Assign (totes)"/>
     <tableColumn id="5" xr3:uid="{A807D77C-1601-4F0D-84F5-381B6F03AC1B}" name="Process Scans (cases)"/>
+    <tableColumn id="7" xr3:uid="{B3284CE8-32A7-914E-869A-6C94DCED56FF}" name="Capture Item Attribute"/>
     <tableColumn id="6" xr3:uid="{D0114EA9-267B-4479-AE26-CCD54F9A1017}" name="Split Case (units)"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -327,14 +328,15 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{4512BFD2-5E13-4737-83C0-9B41775FB93F}" name="Table10" displayName="Table10" ref="A1:F62" totalsRowShown="0">
-  <autoFilter ref="A1:F62" xr:uid="{4512BFD2-5E13-4737-83C0-9B41775FB93F}"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{4512BFD2-5E13-4737-83C0-9B41775FB93F}" name="Table10" displayName="Table10" ref="A1:G62" totalsRowShown="0">
+  <autoFilter ref="A1:G62" xr:uid="{4512BFD2-5E13-4737-83C0-9B41775FB93F}"/>
+  <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{08588F7D-1EF6-49C7-B58C-1A3A5206C368}" name="TM"/>
     <tableColumn id="2" xr3:uid="{B13F0FE7-216A-4B8C-8221-EFC298E29016}" name="Shift"/>
     <tableColumn id="3" xr3:uid="{B17C3F1E-52A7-4EDA-901E-420A077C19B1}" name="Palletize (units)"/>
     <tableColumn id="4" xr3:uid="{91231D20-57BE-4DCD-8344-5423CF2304F8}" name="Zone Assign (totes)"/>
     <tableColumn id="5" xr3:uid="{8880296B-7DEB-4B79-9B63-1E9100891524}" name="Process Scans (cases)"/>
+    <tableColumn id="7" xr3:uid="{366B6915-632A-C448-8A36-2683D81C8BE4}" name="Capture Item Attribute"/>
     <tableColumn id="6" xr3:uid="{EB8784C3-068E-42F7-AC7B-912F9BEF1B25}" name="Split Case (units)"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -342,14 +344,15 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{F14F4019-76F5-431E-8854-A68F62B3CD20}" name="Table12" displayName="Table12" ref="A1:F62" totalsRowShown="0">
-  <autoFilter ref="A1:F62" xr:uid="{F14F4019-76F5-431E-8854-A68F62B3CD20}"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{F14F4019-76F5-431E-8854-A68F62B3CD20}" name="Table12" displayName="Table12" ref="A1:G62" totalsRowShown="0">
+  <autoFilter ref="A1:G62" xr:uid="{F14F4019-76F5-431E-8854-A68F62B3CD20}"/>
+  <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{60CDDD39-DEA2-43C9-B8A8-CCFDAC4F2BC9}" name="TM"/>
     <tableColumn id="2" xr3:uid="{E2371ED5-FB7F-462B-9B8C-4E7667D31BDF}" name="Shift"/>
     <tableColumn id="3" xr3:uid="{DBFE3C75-17CE-40A4-926C-6B10856796DE}" name="Palletize (units)"/>
     <tableColumn id="4" xr3:uid="{AF47C441-8BAD-4DCC-8335-BD8988EB0210}" name="Zone Assign (totes)"/>
     <tableColumn id="5" xr3:uid="{CBB610D5-550C-44F0-810C-5D5B11520A9B}" name="Process Scans (cases)"/>
+    <tableColumn id="7" xr3:uid="{C6387C1E-5719-EE4C-BD3B-E97B07EB28A1}" name="Capture Item Attribute"/>
     <tableColumn id="6" xr3:uid="{A3B5AA86-F000-42EA-9642-15ED477DD4D5}" name="Split Case (units)"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -357,14 +360,15 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{AA15E6A3-EEFC-48BA-8577-93E1FB25341C}" name="Table13" displayName="Table13" ref="A1:F62" totalsRowShown="0">
-  <autoFilter ref="A1:F62" xr:uid="{AA15E6A3-EEFC-48BA-8577-93E1FB25341C}"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{AA15E6A3-EEFC-48BA-8577-93E1FB25341C}" name="Table13" displayName="Table13" ref="A1:G62" totalsRowShown="0">
+  <autoFilter ref="A1:G62" xr:uid="{AA15E6A3-EEFC-48BA-8577-93E1FB25341C}"/>
+  <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{547004EC-846D-43B1-BE9C-07B6A6687B72}" name="TM"/>
     <tableColumn id="2" xr3:uid="{D8F9CD33-889F-4A56-816F-0CFD280D72BD}" name="Shift"/>
     <tableColumn id="3" xr3:uid="{94E8FCFC-464D-4C66-8FEC-305ECCAAC19D}" name="Palletize (units)"/>
     <tableColumn id="4" xr3:uid="{B10B6C53-8FAE-487E-92A3-3E143147C99A}" name="Zone Assign (totes)"/>
     <tableColumn id="5" xr3:uid="{279A722D-9004-4F29-9018-A7AD61FA5EB6}" name="Process Scans (cases)"/>
+    <tableColumn id="7" xr3:uid="{FB55D83C-8138-8C48-B45A-ABB88FEA73F8}" name="Capture Item Attribute"/>
     <tableColumn id="6" xr3:uid="{03F08BB9-DBDB-4566-843C-8037A7575EDB}" name="Split Case (units)"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -468,14 +472,15 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{EC240D53-8973-4595-B9AA-EBD5DC4058AE}" name="Table8" displayName="Table8" ref="A1:F62" totalsRowShown="0">
-  <autoFilter ref="A1:F62" xr:uid="{EC240D53-8973-4595-B9AA-EBD5DC4058AE}"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{EC240D53-8973-4595-B9AA-EBD5DC4058AE}" name="Table8" displayName="Table8" ref="A1:G62" totalsRowShown="0">
+  <autoFilter ref="A1:G62" xr:uid="{EC240D53-8973-4595-B9AA-EBD5DC4058AE}"/>
+  <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{9E50C632-B7C8-4356-AAE1-B59808AEDA0E}" name="TM"/>
     <tableColumn id="2" xr3:uid="{1856F21C-6D01-482C-A6E3-45AAAC89CC6B}" name="Shift"/>
     <tableColumn id="3" xr3:uid="{F0F35432-415A-41EA-98E9-EC5A0F864D14}" name="Palletize (units)"/>
     <tableColumn id="4" xr3:uid="{A351738A-2C31-48F6-9372-9087AC67B5DA}" name="Zone Assign (totes)"/>
     <tableColumn id="5" xr3:uid="{58DB08F6-8783-4EC8-A6BA-802D0824E2EF}" name="Process Scans (cases)"/>
+    <tableColumn id="7" xr3:uid="{C2D3EBBA-90E6-604A-814F-56054F2D73B6}" name="Capture Item Attribute"/>
     <tableColumn id="6" xr3:uid="{994E2E94-FBA4-4745-9A52-72E573B6F840}" name="Split Case (units)"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -483,14 +488,15 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{1F5C3D6F-CF80-4691-A1F0-8A29432735A2}" name="Table9" displayName="Table9" ref="A1:F62" totalsRowShown="0">
-  <autoFilter ref="A1:F62" xr:uid="{1F5C3D6F-CF80-4691-A1F0-8A29432735A2}"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{1F5C3D6F-CF80-4691-A1F0-8A29432735A2}" name="Table9" displayName="Table9" ref="A1:G62" totalsRowShown="0">
+  <autoFilter ref="A1:G62" xr:uid="{1F5C3D6F-CF80-4691-A1F0-8A29432735A2}"/>
+  <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{7A0188B7-50B3-4977-A0FA-EC9A1A06161B}" name="TM"/>
     <tableColumn id="2" xr3:uid="{14AE62D3-42D5-4B5D-854D-F34334DDA517}" name="Shift"/>
     <tableColumn id="3" xr3:uid="{1080F001-A6D3-4DC0-A452-150C51646DBF}" name="Palletize (units)"/>
     <tableColumn id="4" xr3:uid="{9A5B4169-BAC0-4047-9DAE-2A3FDA1CCB42}" name="Zone Assign (totes)"/>
     <tableColumn id="5" xr3:uid="{390EDBEE-1A50-4119-9BDF-6A750009E68A}" name="Process Scans (cases)"/>
+    <tableColumn id="7" xr3:uid="{EF97A384-5F02-6B44-AB38-D1383BDFE7C4}" name="Capture Item Attribute"/>
     <tableColumn id="6" xr3:uid="{4E806D02-B26A-4E44-B4EE-9CEA3D97C0AB}" name="Split Case (units)"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -814,18 +820,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74E1F963-EC4F-414D-8598-E8A6218B2DBE}">
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.72265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.3984375" customWidth="1"/>
     <col min="3" max="3" width="17.21875" customWidth="1"/>
     <col min="4" max="4" width="20.4453125" customWidth="1"/>
-    <col min="5" max="5" width="23" customWidth="1"/>
-    <col min="6" max="6" width="18.6953125" customWidth="1"/>
+    <col min="5" max="6" width="23" customWidth="1"/>
+    <col min="7" max="7" width="18.6953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -842,10 +848,13 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -864,8 +873,11 @@
       <c r="F2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -884,8 +896,11 @@
       <c r="F3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -904,8 +919,11 @@
       <c r="F4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -924,8 +942,11 @@
       <c r="F5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -944,8 +965,11 @@
       <c r="F6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -964,8 +988,11 @@
       <c r="F7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -984,8 +1011,11 @@
       <c r="F8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -1004,8 +1034,11 @@
       <c r="F9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -1024,8 +1057,11 @@
       <c r="F10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -1044,8 +1080,11 @@
       <c r="F11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -1064,8 +1103,11 @@
       <c r="F12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -1084,8 +1126,11 @@
       <c r="F13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -1104,8 +1149,11 @@
       <c r="F14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -1124,8 +1172,11 @@
       <c r="F15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -1144,8 +1195,11 @@
       <c r="F16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -1164,8 +1218,11 @@
       <c r="F17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -1184,8 +1241,11 @@
       <c r="F18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -1204,8 +1264,11 @@
       <c r="F19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -1224,8 +1287,11 @@
       <c r="F20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>27</v>
       </c>
@@ -1244,8 +1310,11 @@
       <c r="F21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>68</v>
       </c>
@@ -1264,8 +1333,11 @@
       <c r="F22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -1284,8 +1356,11 @@
       <c r="F23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -1304,8 +1379,11 @@
       <c r="F24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>30</v>
       </c>
@@ -1324,8 +1402,11 @@
       <c r="F25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>31</v>
       </c>
@@ -1344,8 +1425,11 @@
       <c r="F26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -1364,8 +1448,11 @@
       <c r="F27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -1384,8 +1471,11 @@
       <c r="F28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>34</v>
       </c>
@@ -1404,8 +1494,11 @@
       <c r="F29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>35</v>
       </c>
@@ -1424,8 +1517,11 @@
       <c r="F30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>36</v>
       </c>
@@ -1444,8 +1540,11 @@
       <c r="F31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>37</v>
       </c>
@@ -1464,8 +1563,11 @@
       <c r="F32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>38</v>
       </c>
@@ -1484,8 +1586,11 @@
       <c r="F33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>41</v>
       </c>
@@ -1504,8 +1609,11 @@
       <c r="F34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>42</v>
       </c>
@@ -1524,8 +1632,11 @@
       <c r="F35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>43</v>
       </c>
@@ -1544,8 +1655,11 @@
       <c r="F36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>44</v>
       </c>
@@ -1564,8 +1678,11 @@
       <c r="F37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>45</v>
       </c>
@@ -1584,8 +1701,11 @@
       <c r="F38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>46</v>
       </c>
@@ -1604,8 +1724,11 @@
       <c r="F39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>47</v>
       </c>
@@ -1624,8 +1747,11 @@
       <c r="F40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>67</v>
       </c>
@@ -1644,8 +1770,11 @@
       <c r="F41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>49</v>
       </c>
@@ -1664,8 +1793,11 @@
       <c r="F42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>50</v>
       </c>
@@ -1684,8 +1816,11 @@
       <c r="F43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>51</v>
       </c>
@@ -1704,8 +1839,11 @@
       <c r="F44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>52</v>
       </c>
@@ -1724,8 +1862,11 @@
       <c r="F45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>53</v>
       </c>
@@ -1744,8 +1885,11 @@
       <c r="F46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>54</v>
       </c>
@@ -1764,8 +1908,11 @@
       <c r="F47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>55</v>
       </c>
@@ -1784,8 +1931,11 @@
       <c r="F48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>56</v>
       </c>
@@ -1804,8 +1954,11 @@
       <c r="F49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>57</v>
       </c>
@@ -1824,8 +1977,11 @@
       <c r="F50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>58</v>
       </c>
@@ -1844,8 +2000,11 @@
       <c r="F51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>59</v>
       </c>
@@ -1864,8 +2023,11 @@
       <c r="F52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>60</v>
       </c>
@@ -1884,8 +2046,11 @@
       <c r="F53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -1904,8 +2069,11 @@
       <c r="F54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>40</v>
       </c>
@@ -1924,8 +2092,11 @@
       <c r="F55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>62</v>
       </c>
@@ -1944,8 +2115,11 @@
       <c r="F56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>63</v>
       </c>
@@ -1964,8 +2138,11 @@
       <c r="F57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>64</v>
       </c>
@@ -1984,8 +2161,11 @@
       <c r="F58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>65</v>
       </c>
@@ -2004,8 +2184,11 @@
       <c r="F59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>66</v>
       </c>
@@ -2022,6 +2205,9 @@
         <v>0</v>
       </c>
       <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
         <v>0</v>
       </c>
     </row>
@@ -2036,17 +2222,17 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C739F3D5-5D78-4E86-8CF1-7B5A1F05E574}">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.72265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.21875" customWidth="1"/>
     <col min="4" max="4" width="20.4453125" customWidth="1"/>
-    <col min="5" max="5" width="23" customWidth="1"/>
-    <col min="6" max="6" width="18.6953125" customWidth="1"/>
+    <col min="5" max="6" width="23" customWidth="1"/>
+    <col min="7" max="7" width="18.6953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2063,10 +2249,13 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -2074,7 +2263,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -2082,7 +2271,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2090,7 +2279,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -2098,7 +2287,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -2106,7 +2295,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2114,7 +2303,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -2122,7 +2311,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -2130,7 +2319,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -2138,7 +2327,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -2146,7 +2335,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -2154,7 +2343,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -2162,7 +2351,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -2170,7 +2359,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -2178,7 +2367,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -2564,17 +2753,17 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA1554B1-802D-4A20-BC26-F8BA227759BF}">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.72265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.21875" customWidth="1"/>
     <col min="4" max="4" width="20.4453125" customWidth="1"/>
-    <col min="5" max="5" width="23" customWidth="1"/>
-    <col min="6" max="6" width="18.6953125" customWidth="1"/>
+    <col min="5" max="6" width="23" customWidth="1"/>
+    <col min="7" max="7" width="18.6953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2591,10 +2780,13 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -2602,7 +2794,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -2610,7 +2802,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2618,7 +2810,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -2626,7 +2818,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -2634,7 +2826,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2642,7 +2834,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -2650,7 +2842,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -2658,7 +2850,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -2666,7 +2858,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -2674,7 +2866,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -2682,7 +2874,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -2690,7 +2882,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -2698,7 +2890,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -2706,7 +2898,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -3092,17 +3284,17 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24A03AE5-8B34-461C-82D3-94D0135A97AF}">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.72265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.21875" customWidth="1"/>
     <col min="4" max="4" width="20.4453125" customWidth="1"/>
-    <col min="5" max="5" width="23" customWidth="1"/>
-    <col min="6" max="6" width="18.6953125" customWidth="1"/>
+    <col min="5" max="6" width="23" customWidth="1"/>
+    <col min="7" max="7" width="18.6953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3119,10 +3311,13 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -3130,7 +3325,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -3138,7 +3333,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -3146,7 +3341,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -3154,7 +3349,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -3162,7 +3357,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -3170,7 +3365,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -3178,7 +3373,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -3186,7 +3381,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -3194,7 +3389,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -3202,7 +3397,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -3210,7 +3405,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -3218,7 +3413,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -3226,7 +3421,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -3234,7 +3429,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -10714,7 +10909,7 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -10722,7 +10917,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -11159,17 +11354,17 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18D726EA-BA80-415E-B2ED-BE7FDDB5EC80}">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.72265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.21875" customWidth="1"/>
     <col min="4" max="4" width="20.4453125" customWidth="1"/>
-    <col min="5" max="5" width="23" customWidth="1"/>
-    <col min="6" max="6" width="18.6953125" customWidth="1"/>
+    <col min="5" max="6" width="23" customWidth="1"/>
+    <col min="7" max="7" width="18.6953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -11186,10 +11381,13 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -11197,7 +11395,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -11205,7 +11403,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -11213,7 +11411,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -11221,7 +11419,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -11229,7 +11427,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -11237,23 +11435,23 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -11261,7 +11459,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -11269,7 +11467,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -11277,7 +11475,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -11285,7 +11483,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -11293,7 +11491,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -11301,7 +11499,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -11687,17 +11885,17 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9347B211-E4AA-4392-9A89-748D39049813}">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.72265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.21875" customWidth="1"/>
     <col min="4" max="4" width="20.4453125" customWidth="1"/>
-    <col min="5" max="5" width="23" customWidth="1"/>
-    <col min="6" max="6" width="18.6953125" customWidth="1"/>
+    <col min="5" max="6" width="23" customWidth="1"/>
+    <col min="7" max="7" width="18.6953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -11714,10 +11912,13 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -11725,7 +11926,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -11733,7 +11934,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -11741,7 +11942,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -11749,7 +11950,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -11757,7 +11958,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -11765,7 +11966,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -11773,7 +11974,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -11781,7 +11982,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -11789,7 +11990,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -11797,7 +11998,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -11805,7 +12006,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -11813,7 +12014,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -11821,7 +12022,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -11829,7 +12030,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>21</v>
       </c>
